--- a/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/01_MasterData.xlsx
+++ b/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/01_MasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kandilglass20-my.sharepoint.com/personal/ahmed_fergany_kandilglass_com/Documents/Attachments/GitHub/Final_Learning_AI/05_Machine_Learning/01_DataEngineering/GraduationProjects/FactoryTwo/ExcelTemplateStandards/DataEntry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_E8677F28B73FD4DDB9E20C810D04293B11DFBCF4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E692B223-3745-45F2-AE40-4324BE874D1B}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_E8677F28B73FD4DDB9E20C810D04293B11DFBCF4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9DC1DB-161F-436E-B910-7F06D7137629}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -599,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -626,7 +626,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -635,12 +634,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2862,17 +2860,17 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2894,52 +2892,52 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2960,52 +2958,52 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3026,52 +3024,52 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3092,52 +3090,52 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3165,28 +3163,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="4" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -3417,18 +3415,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3508,20 +3506,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3613,20 +3611,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3671,26 +3669,26 @@
       <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="24">
         <v>98000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="24">
         <v>45000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -3699,12 +3697,12 @@
       <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="24">
         <v>210000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>103</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -3713,12 +3711,12 @@
       <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="24">
         <v>150000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="8" t="s">
         <v>104</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -3727,12 +3725,12 @@
       <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="24">
         <v>88000</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>105</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -3741,21 +3739,21 @@
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="24">
         <v>320000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>175000</v>
       </c>
     </row>
@@ -3763,19 +3761,19 @@
       <c r="A13" s="8"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="28"/>
+      <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="28"/>
+      <c r="D14" s="24"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="29"/>
+      <c r="D15" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3800,18 +3798,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3836,7 +3834,7 @@
       <c r="B5" s="7">
         <v>1.5</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>0.5</v>
       </c>
     </row>
@@ -3847,7 +3845,7 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>1</v>
       </c>
     </row>
@@ -3858,7 +3856,7 @@
       <c r="B7" s="7">
         <v>6</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>2</v>
       </c>
     </row>
@@ -3866,10 +3864,10 @@
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>8</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <v>3</v>
       </c>
     </row>
@@ -3896,18 +3894,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4003,17 +4001,17 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4031,22 +4029,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4067,22 +4065,22 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>85</v>
       </c>
     </row>
